--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.7750,0.0419,0.1580,0.0139</t>
-  </si>
-  <si>
-    <t>0.7623,0.0224,0.1062,0.0325</t>
-  </si>
-  <si>
-    <t>0.8097,0.0254,0.0884,0.0213</t>
-  </si>
-  <si>
-    <t>0.7685,0.0312,0.1588,0.0123</t>
-  </si>
-  <si>
-    <t>0.6981,0.0516,0.1485,0.0460</t>
-  </si>
-  <si>
-    <t>0.7446,0.0611,0.1144,0.0303</t>
-  </si>
-  <si>
-    <t>0.6609,0.0263,0.1135,0.0892</t>
-  </si>
-  <si>
-    <t>0.6915,0.0826,0.1285,0.0409</t>
-  </si>
-  <si>
-    <t>0.7303,0.0485,0.1260,0.0380</t>
-  </si>
-  <si>
-    <t>0.6480,0.0685,0.1207,0.0963</t>
-  </si>
-  <si>
-    <t>0.7003,0.0718,0.1126,0.0565</t>
-  </si>
-  <si>
-    <t>0.6938,0.0552,0.1773,0.0321</t>
-  </si>
-  <si>
-    <t>0.8403,0.0364,0.1392,0.0038</t>
-  </si>
-  <si>
-    <t>0.7365,0.0234,0.3056,0.0054</t>
-  </si>
-  <si>
-    <t>0.7109,0.0182,0.4178,0.0039</t>
-  </si>
-  <si>
-    <t>0.6447,0.0290,0.4823,0.0036</t>
-  </si>
-  <si>
-    <t>0.7739,0.0654,0.1955,0.0082</t>
-  </si>
-  <si>
-    <t>0.2505,0.7409,0.1494,0.0083</t>
-  </si>
-  <si>
-    <t>0.5878,0.3076,0.2082,0.0077</t>
-  </si>
-  <si>
-    <t>0.7053,0.1124,0.1823,0.0141</t>
-  </si>
-  <si>
-    <t>0.4519,0.3793,0.2956,0.0198</t>
-  </si>
-  <si>
-    <t>0.6295,0.2579,0.1920,0.0061</t>
-  </si>
-  <si>
-    <t>0.7224,0.0413,0.3021,0.0091</t>
-  </si>
-  <si>
-    <t>0.8518,0.0222,0.1169,0.0058</t>
-  </si>
-  <si>
-    <t>0.7693,0.0288,0.2077,0.0085</t>
-  </si>
-  <si>
-    <t>0.7225,0.0516,0.2836,0.0070</t>
-  </si>
-  <si>
-    <t>0.7397,0.0357,0.2681,0.0081</t>
-  </si>
-  <si>
-    <t>0.6720,0.0349,0.4166,0.0071</t>
-  </si>
-  <si>
-    <t>0.5049,0.0214,0.6363,0.0047</t>
-  </si>
-  <si>
-    <t>0.6275,0.1630,0.3067,0.0079</t>
-  </si>
-  <si>
-    <t>0.7012,0.0967,0.1769,0.0287</t>
-  </si>
-  <si>
-    <t>0.2756,0.2113,0.7012,0.0195</t>
-  </si>
-  <si>
-    <t>0.6557,0.1346,0.2677,0.0123</t>
-  </si>
-  <si>
-    <t>0.6943,0.0402,0.1398,0.0475</t>
-  </si>
-  <si>
-    <t>0.6871,0.0887,0.2221,0.0249</t>
-  </si>
-  <si>
-    <t>0.6906,0.0659,0.1892,0.0278</t>
-  </si>
-  <si>
-    <t>0.7489,0.0814,0.1465,0.0136</t>
-  </si>
-  <si>
-    <t>0.5917,0.2607,0.1255,0.0055</t>
-  </si>
-  <si>
-    <t>0.8061,0.0211,0.2000,0.0021</t>
-  </si>
-  <si>
-    <t>0.6740,0.0373,0.3470,0.0039</t>
-  </si>
-  <si>
-    <t>0.6926,0.0173,0.3647,0.0093</t>
-  </si>
-  <si>
-    <t>0.7471,0.0398,0.2532,0.0031</t>
-  </si>
-  <si>
-    <t>0.6042,0.3335,0.0891,0.0064</t>
-  </si>
-  <si>
-    <t>0.7000,0.0200,0.3744,0.0041</t>
-  </si>
-  <si>
-    <t>0.7975,0.0598,0.1642,0.0086</t>
-  </si>
-  <si>
-    <t>0.5600,0.4285,0.0993,0.0054</t>
-  </si>
-  <si>
-    <t>0.5315,0.4138,0.1498,0.0058</t>
-  </si>
-  <si>
-    <t>0.4811,0.4715,0.1631,0.0057</t>
-  </si>
-  <si>
-    <t>0.4328,0.0965,0.5374,0.0078</t>
-  </si>
-  <si>
-    <t>0.3797,0.0757,0.6821,0.0098</t>
-  </si>
-  <si>
-    <t>0.6276,0.0267,0.4420,0.0042</t>
-  </si>
-  <si>
-    <t>0.7015,0.0233,0.3477,0.0088</t>
-  </si>
-  <si>
-    <t>0.3899,0.0381,0.7328,0.0060</t>
-  </si>
-  <si>
-    <t>0.5725,0.1056,0.4145,0.0080</t>
-  </si>
-  <si>
-    <t>0.6837,0.0837,0.2161,0.0231</t>
-  </si>
-  <si>
-    <t>0.7320,0.0643,0.1873,0.0157</t>
-  </si>
-  <si>
-    <t>0.7018,0.0620,0.2181,0.0220</t>
-  </si>
-  <si>
-    <t>0.6039,0.1274,0.3498,0.0162</t>
-  </si>
-  <si>
-    <t>0.7355,0.0612,0.1551,0.0219</t>
-  </si>
-  <si>
-    <t>0.6610,0.0670,0.1690,0.0557</t>
-  </si>
-  <si>
-    <t>0.7717,0.0461,0.1188,0.0197</t>
-  </si>
-  <si>
-    <t>0.4050,0.2732,0.2819,0.0030</t>
-  </si>
-  <si>
-    <t>0.5252,0.0461,0.5695,0.0060</t>
-  </si>
-  <si>
-    <t>0.7128,0.0283,0.3501,0.0036</t>
-  </si>
-  <si>
-    <t>0.3568,0.2944,0.3571,0.0032</t>
-  </si>
-  <si>
-    <t>0.3107,0.0763,0.7479,0.0108</t>
-  </si>
-  <si>
-    <t>0.7864,0.0769,0.1269,0.0109</t>
-  </si>
-  <si>
-    <t>0.0458,0.9613,0.0390,0.0011</t>
-  </si>
-  <si>
-    <t>0.7920,0.0475,0.1306,0.0126</t>
-  </si>
-  <si>
-    <t>0.7747,0.0379,0.1289,0.0174</t>
-  </si>
-  <si>
-    <t>0.5512,0.0873,0.5184,0.0090</t>
-  </si>
-  <si>
-    <t>0.4791,0.3204,0.1785,0.0032</t>
-  </si>
-  <si>
-    <t>0.6654,0.0833,0.2367,0.0024</t>
-  </si>
-  <si>
-    <t>0.2070,0.7284,0.0976,0.0018</t>
-  </si>
-  <si>
-    <t>0.3515,0.2184,0.3944,0.0026</t>
-  </si>
-  <si>
-    <t>0.7879,0.0145,0.1292,0.0161</t>
-  </si>
-  <si>
-    <t>0.7749,0.0305,0.1228,0.0244</t>
-  </si>
-  <si>
-    <t>0.8069,0.0370,0.1069,0.0189</t>
-  </si>
-  <si>
-    <t>0.7857,0.0242,0.1003,0.0289</t>
-  </si>
-  <si>
-    <t>0.8143,0.0234,0.1294,0.0092</t>
-  </si>
-  <si>
-    <t>0.7992,0.0297,0.1354,0.0151</t>
-  </si>
-  <si>
-    <t>0.3543,0.2348,0.4766,0.0074</t>
-  </si>
-  <si>
-    <t>0.5520,0.0752,0.4370,0.0052</t>
-  </si>
-  <si>
-    <t>0.5269,0.2098,0.2198,0.0025</t>
-  </si>
-  <si>
-    <t>0.4745,0.1274,0.5079,0.0070</t>
-  </si>
-  <si>
-    <t>0.3338,0.1959,0.5518,0.0080</t>
-  </si>
-  <si>
-    <t>0.5444,0.1338,0.3497,0.0047</t>
-  </si>
-  <si>
-    <t>0.7186,0.0462,0.0907,0.0628</t>
-  </si>
-  <si>
-    <t>0.7148,0.0903,0.1509,0.0230</t>
-  </si>
-  <si>
-    <t>0.7706,0.0611,0.1284,0.0139</t>
-  </si>
-  <si>
-    <t>0.7370,0.0608,0.1147,0.0329</t>
-  </si>
-  <si>
-    <t>0.7009,0.0682,0.1553,0.0404</t>
-  </si>
-  <si>
-    <t>0.6792,0.0713,0.1584,0.0473</t>
-  </si>
-  <si>
-    <t>0.7539,0.0362,0.1358,0.0239</t>
-  </si>
-  <si>
-    <t>0.6793,0.0713,0.1516,0.0436</t>
-  </si>
-  <si>
-    <t>0.7493,0.0390,0.0736,0.0567</t>
-  </si>
-  <si>
-    <t>0.7295,0.0405,0.1044,0.0540</t>
-  </si>
-  <si>
-    <t>0.7843,0.0492,0.0957,0.0194</t>
-  </si>
-  <si>
-    <t>0.6912,0.0718,0.1221,0.0591</t>
-  </si>
-  <si>
-    <t>0.7098,0.0460,0.1056,0.0453</t>
-  </si>
-  <si>
-    <t>0.8141,0.0340,0.0626,0.0261</t>
-  </si>
-  <si>
-    <t>0.7374,0.0371,0.1249,0.0332</t>
-  </si>
-  <si>
-    <t>0.7133,0.0446,0.1104,0.0465</t>
-  </si>
-  <si>
-    <t>0.1670,0.0514,0.8926,0.0028</t>
-  </si>
-  <si>
-    <t>0.7512,0.0483,0.2407,0.0030</t>
-  </si>
-  <si>
-    <t>0.7964,0.0332,0.1460,0.0145</t>
-  </si>
-  <si>
-    <t>0.6531,0.0312,0.4003,0.0103</t>
-  </si>
-  <si>
-    <t>0.7627,0.1117,0.1490,0.0083</t>
-  </si>
-  <si>
-    <t>0.6500,0.1525,0.2649,0.0106</t>
-  </si>
-  <si>
-    <t>0.6916,0.1161,0.1851,0.0242</t>
-  </si>
-  <si>
-    <t>0.6867,0.1408,0.2115,0.0136</t>
-  </si>
-  <si>
-    <t>0.7314,0.0933,0.1782,0.0152</t>
-  </si>
-  <si>
-    <t>0.5657,0.2973,0.2193,0.0101</t>
-  </si>
-  <si>
-    <t>0.7484,0.0672,0.1458,0.0199</t>
-  </si>
-  <si>
-    <t>0.7566,0.0683,0.1582,0.0178</t>
-  </si>
-  <si>
-    <t>0.6958,0.0411,0.3297,0.0147</t>
-  </si>
-  <si>
-    <t>0.7377,0.0606,0.2460,0.0090</t>
-  </si>
-  <si>
-    <t>0.8321,0.0377,0.1093,0.0068</t>
-  </si>
-  <si>
-    <t>0.7530,0.0405,0.1482,0.0217</t>
-  </si>
-  <si>
-    <t>0.5256,0.4903,0.0892,0.0046</t>
-  </si>
-  <si>
-    <t>0.4638,0.5286,0.1119,0.0067</t>
-  </si>
-  <si>
-    <t>0.7396,0.1162,0.1822,0.0091</t>
-  </si>
-  <si>
-    <t>0.4279,0.5125,0.2121,0.0086</t>
-  </si>
-  <si>
-    <t>0.6872,0.1090,0.1696,0.0245</t>
-  </si>
-  <si>
-    <t>0.7377,0.0337,0.1126,0.0421</t>
-  </si>
-  <si>
-    <t>0.7728,0.0515,0.1299,0.0219</t>
-  </si>
-  <si>
-    <t>0.7885,0.0375,0.1022,0.0181</t>
-  </si>
-  <si>
-    <t>0.7416,0.0339,0.1900,0.0182</t>
-  </si>
-  <si>
-    <t>0.7466,0.0378,0.1080,0.0391</t>
-  </si>
-  <si>
-    <t>0.7842,0.0397,0.1525,0.0103</t>
-  </si>
-  <si>
-    <t>0.7218,0.0535,0.1377,0.0431</t>
-  </si>
-  <si>
-    <t>0.7721,0.0499,0.1142,0.0243</t>
-  </si>
-  <si>
-    <t>0.7690,0.0473,0.1058,0.0267</t>
-  </si>
-  <si>
-    <t>0.7447,0.0482,0.1300,0.0243</t>
-  </si>
-  <si>
-    <t>0.4269,0.2932,0.2832,0.0049</t>
-  </si>
-  <si>
-    <t>0.4948,0.1198,0.4736,0.0068</t>
-  </si>
-  <si>
-    <t>0.4512,0.3463,0.1624,0.0035</t>
-  </si>
-  <si>
-    <t>0.6896,0.0341,0.3989,0.0032</t>
-  </si>
-  <si>
-    <t>0.8194,0.0147,0.1802,0.0046</t>
-  </si>
-  <si>
-    <t>0.7589,0.0210,0.1723,0.0150</t>
-  </si>
-  <si>
-    <t>0.6861,0.0457,0.3065,0.0140</t>
-  </si>
-  <si>
-    <t>0.8018,0.0668,0.1360,0.0089</t>
-  </si>
-  <si>
-    <t>0.8012,0.0185,0.1700,0.0094</t>
-  </si>
-  <si>
-    <t>0.6059,0.0208,0.0589,0.2362</t>
-  </si>
-  <si>
-    <t>0.8242,0.0122,0.0565,0.0270</t>
-  </si>
-  <si>
-    <t>0.7758,0.0299,0.1052,0.0296</t>
-  </si>
-  <si>
-    <t>0.0534,0.8487,0.3117,0.0041</t>
-  </si>
-  <si>
-    <t>0.7168,0.0632,0.1444,0.0356</t>
-  </si>
-  <si>
-    <t>0.7675,0.0652,0.1793,0.0075</t>
-  </si>
-  <si>
-    <t>0.7293,0.0417,0.1424,0.0375</t>
-  </si>
-  <si>
-    <t>0.7529,0.0713,0.1407,0.0178</t>
-  </si>
-  <si>
-    <t>0.7336,0.0435,0.1940,0.0201</t>
-  </si>
-  <si>
-    <t>0.7905,0.0346,0.1349,0.0124</t>
-  </si>
-  <si>
-    <t>0.7218,0.0526,0.1104,0.0495</t>
-  </si>
-  <si>
-    <t>0.2456,0.2037,0.7427,0.0236</t>
-  </si>
-  <si>
-    <t>0.7410,0.0516,0.1337,0.0298</t>
-  </si>
-  <si>
-    <t>0.7769,0.0417,0.0910,0.0319</t>
-  </si>
-  <si>
-    <t>0.7884,0.0375,0.1042,0.0192</t>
-  </si>
-  <si>
-    <t>0.7776,0.0384,0.1067,0.0258</t>
-  </si>
-  <si>
-    <t>0.7889,0.0355,0.1361,0.0104</t>
-  </si>
-  <si>
-    <t>0.7081,0.0975,0.2137,0.0161</t>
-  </si>
-  <si>
-    <t>0.7639,0.0652,0.1766,0.0122</t>
-  </si>
-  <si>
-    <t>0.7254,0.0867,0.1906,0.0154</t>
-  </si>
-  <si>
-    <t>0.7143,0.0567,0.1783,0.0286</t>
-  </si>
-  <si>
-    <t>0.6865,0.0776,0.1324,0.0468</t>
-  </si>
-  <si>
-    <t>0.7340,0.0379,0.1229,0.0358</t>
-  </si>
-  <si>
-    <t>0.7466,0.0517,0.1064,0.0372</t>
-  </si>
-  <si>
-    <t>0.7100,0.0680,0.1631,0.0402</t>
-  </si>
-  <si>
-    <t>0.6847,0.0707,0.1377,0.0502</t>
-  </si>
-  <si>
-    <t>0.7366,0.0443,0.1329,0.0345</t>
-  </si>
-  <si>
-    <t>0.7611,0.0304,0.0679,0.0480</t>
-  </si>
-  <si>
-    <t>0.6878,0.1146,0.1902,0.0197</t>
-  </si>
-  <si>
-    <t>0.7351,0.0670,0.1624,0.0182</t>
-  </si>
-  <si>
-    <t>0.6669,0.1797,0.2217,0.0165</t>
-  </si>
-  <si>
-    <t>0.6555,0.0661,0.2924,0.0252</t>
-  </si>
-  <si>
-    <t>0.6879,0.0731,0.1254,0.0458</t>
-  </si>
-  <si>
-    <t>0.7833,0.0456,0.0890,0.0279</t>
-  </si>
-  <si>
-    <t>0.7345,0.0609,0.1765,0.0230</t>
-  </si>
-  <si>
-    <t>0.7044,0.0416,0.1723,0.0410</t>
-  </si>
-  <si>
-    <t>0.2677,0.0752,0.8182,0.0062</t>
-  </si>
-  <si>
-    <t>0.6976,0.0321,0.1313,0.0500</t>
-  </si>
-  <si>
-    <t>0.6224,0.0546,0.4083,0.0051</t>
-  </si>
-  <si>
-    <t>0.5808,0.0277,0.5298,0.0056</t>
-  </si>
-  <si>
-    <t>0.7186,0.0230,0.3100,0.0052</t>
-  </si>
-  <si>
-    <t>0.7847,0.0679,0.1399,0.0046</t>
-  </si>
-  <si>
-    <t>0.7878,0.0162,0.2705,0.0028</t>
-  </si>
-  <si>
-    <t>0.7170,0.0395,0.3197,0.0053</t>
-  </si>
-  <si>
-    <t>0.3876,0.0932,0.6547,0.0054</t>
-  </si>
-  <si>
-    <t>0.7331,0.0258,0.2817,0.0077</t>
-  </si>
-  <si>
-    <t>0.6780,0.0272,0.4010,0.0071</t>
-  </si>
-  <si>
-    <t>0.6635,0.0974,0.2869,0.0136</t>
-  </si>
-  <si>
-    <t>0.6851,0.1191,0.2302,0.0102</t>
-  </si>
-  <si>
-    <t>0.7903,0.0464,0.1651,0.0074</t>
-  </si>
-  <si>
-    <t>0.7185,0.0510,0.2751,0.0057</t>
-  </si>
-  <si>
-    <t>0.7420,0.0717,0.2153,0.0076</t>
-  </si>
-  <si>
-    <t>0.7112,0.0537,0.2938,0.0084</t>
-  </si>
-  <si>
-    <t>0.6897,0.0663,0.2073,0.0253</t>
-  </si>
-  <si>
-    <t>0.7405,0.0577,0.1411,0.0222</t>
-  </si>
-  <si>
-    <t>0.6647,0.1321,0.1970,0.0279</t>
-  </si>
-  <si>
-    <t>0.7239,0.0516,0.1229,0.0430</t>
-  </si>
-  <si>
-    <t>0.6303,0.1025,0.1561,0.0553</t>
-  </si>
-  <si>
-    <t>0.7063,0.0703,0.2654,0.0124</t>
-  </si>
-  <si>
-    <t>0.7819,0.0294,0.1870,0.0107</t>
-  </si>
-  <si>
-    <t>0.7042,0.0440,0.3174,0.0090</t>
-  </si>
-  <si>
-    <t>0.7875,0.0462,0.1710,0.0068</t>
-  </si>
-  <si>
-    <t>0.7618,0.0430,0.2309,0.0061</t>
-  </si>
-  <si>
-    <t>0.6494,0.0389,0.3923,0.0122</t>
-  </si>
-  <si>
-    <t>0.6573,0.0826,0.3309,0.0077</t>
-  </si>
-  <si>
-    <t>0.6622,0.0218,0.4054,0.0087</t>
-  </si>
-  <si>
-    <t>0.6653,0.0429,0.3647,0.0047</t>
-  </si>
-  <si>
-    <t>0.6056,0.1530,0.2546,0.0043</t>
-  </si>
-  <si>
-    <t>0.7841,0.0434,0.1084,0.0230</t>
-  </si>
-  <si>
-    <t>0.7198,0.0373,0.1108,0.0401</t>
-  </si>
-  <si>
-    <t>0.7327,0.0621,0.1604,0.0223</t>
-  </si>
-  <si>
-    <t>0.7741,0.0492,0.0915,0.0295</t>
-  </si>
-  <si>
-    <t>0.7632,0.0289,0.0949,0.0373</t>
-  </si>
-  <si>
-    <t>0.7220,0.0515,0.1663,0.0275</t>
-  </si>
-  <si>
-    <t>0.7199,0.0728,0.1386,0.0319</t>
-  </si>
-  <si>
-    <t>0.7133,0.0353,0.1026,0.0608</t>
-  </si>
-  <si>
-    <t>0.8376,0.0222,0.0972,0.0116</t>
-  </si>
-  <si>
-    <t>0.6601,0.1057,0.2003,0.0359</t>
-  </si>
-  <si>
-    <t>0.7219,0.0465,0.2300,0.0151</t>
-  </si>
-  <si>
-    <t>0.4891,0.0263,0.6355,0.0048</t>
-  </si>
-  <si>
-    <t>0.4776,0.1082,0.5067,0.0166</t>
-  </si>
-  <si>
-    <t>0.6115,0.0841,0.3951,0.0078</t>
-  </si>
-  <si>
-    <t>0.2165,0.0518,0.8543,0.0047</t>
-  </si>
-  <si>
-    <t>0.6921,0.0501,0.3254,0.0092</t>
-  </si>
-  <si>
-    <t>0.2721,0.0416,0.7984,0.0052</t>
-  </si>
-  <si>
-    <t>0.6789,0.0252,0.4056,0.0039</t>
-  </si>
-  <si>
-    <t>0.6792,0.0534,0.3148,0.0104</t>
-  </si>
-  <si>
-    <t>0.8064,0.0392,0.1494,0.0105</t>
-  </si>
-  <si>
-    <t>0.8160,0.0187,0.1546,0.0086</t>
-  </si>
-  <si>
-    <t>0.8494,0.0228,0.1116,0.0065</t>
-  </si>
-  <si>
-    <t>0.6874,0.0470,0.1224,0.0591</t>
-  </si>
-  <si>
-    <t>0.7128,0.0653,0.1847,0.0292</t>
-  </si>
-  <si>
-    <t>0.6893,0.0563,0.1175,0.0629</t>
-  </si>
-  <si>
-    <t>0.7146,0.0561,0.1436,0.0369</t>
-  </si>
-  <si>
-    <t>0.7214,0.0474,0.1022,0.0634</t>
-  </si>
-  <si>
-    <t>0.7019,0.0526,0.1453,0.0334</t>
-  </si>
-  <si>
-    <t>0.7270,0.0310,0.0870,0.0708</t>
-  </si>
-  <si>
-    <t>0.6424,0.0545,0.0907,0.1075</t>
-  </si>
-  <si>
-    <t>0.6376,0.1208,0.2868,0.0077</t>
-  </si>
-  <si>
-    <t>0.6753,0.0253,0.4095,0.0066</t>
-  </si>
-  <si>
-    <t>0.6109,0.0389,0.4651,0.0034</t>
-  </si>
-  <si>
-    <t>0.6854,0.0595,0.3214,0.0061</t>
-  </si>
-  <si>
-    <t>0.4116,0.0876,0.6259,0.0121</t>
-  </si>
-  <si>
-    <t>0.7887,0.0207,0.2299,0.0049</t>
-  </si>
-  <si>
-    <t>0.6841,0.0519,0.3325,0.0059</t>
-  </si>
-  <si>
-    <t>0.7319,0.0372,0.2237,0.0149</t>
-  </si>
-  <si>
-    <t>0.6990,0.0408,0.1297,0.0555</t>
-  </si>
-  <si>
-    <t>0.8032,0.0368,0.0989,0.0200</t>
-  </si>
-  <si>
-    <t>0.8178,0.0291,0.0909,0.0172</t>
-  </si>
-  <si>
-    <t>0.7797,0.0185,0.0964,0.0279</t>
-  </si>
-  <si>
-    <t>0.7698,0.0111,0.0808,0.0333</t>
-  </si>
-  <si>
-    <t>0.7495,0.0487,0.2068,0.0117</t>
+    <t>0.7911,0.0293,0.1256,0.0199</t>
+  </si>
+  <si>
+    <t>0.7955,0.0285,0.1154,0.0158</t>
+  </si>
+  <si>
+    <t>0.7753,0.0294,0.1052,0.0256</t>
+  </si>
+  <si>
+    <t>0.8254,0.0255,0.1008,0.0122</t>
+  </si>
+  <si>
+    <t>0.7256,0.0378,0.1133,0.0555</t>
+  </si>
+  <si>
+    <t>0.7164,0.0760,0.0981,0.0421</t>
+  </si>
+  <si>
+    <t>0.7456,0.0584,0.1137,0.0284</t>
+  </si>
+  <si>
+    <t>0.6316,0.0479,0.1361,0.0971</t>
+  </si>
+  <si>
+    <t>0.7005,0.1020,0.1218,0.0405</t>
+  </si>
+  <si>
+    <t>0.7108,0.0706,0.1164,0.0435</t>
+  </si>
+  <si>
+    <t>0.7015,0.0655,0.1868,0.0268</t>
+  </si>
+  <si>
+    <t>0.6870,0.0548,0.0882,0.0780</t>
+  </si>
+  <si>
+    <t>0.6981,0.0599,0.2481,0.0155</t>
+  </si>
+  <si>
+    <t>0.7329,0.0609,0.2582,0.0067</t>
+  </si>
+  <si>
+    <t>0.7850,0.0384,0.2262,0.0028</t>
+  </si>
+  <si>
+    <t>0.8110,0.0310,0.2173,0.0036</t>
+  </si>
+  <si>
+    <t>0.6192,0.1757,0.2998,0.0157</t>
+  </si>
+  <si>
+    <t>0.7195,0.1228,0.1501,0.0173</t>
+  </si>
+  <si>
+    <t>0.5824,0.3219,0.1767,0.0058</t>
+  </si>
+  <si>
+    <t>0.6702,0.1372,0.2206,0.0153</t>
+  </si>
+  <si>
+    <t>0.5635,0.3093,0.2282,0.0153</t>
+  </si>
+  <si>
+    <t>0.4192,0.4779,0.2573,0.0110</t>
+  </si>
+  <si>
+    <t>0.7929,0.0242,0.2083,0.0080</t>
+  </si>
+  <si>
+    <t>0.8464,0.0199,0.1366,0.0033</t>
+  </si>
+  <si>
+    <t>0.7289,0.0271,0.3129,0.0063</t>
+  </si>
+  <si>
+    <t>0.7582,0.0370,0.2378,0.0058</t>
+  </si>
+  <si>
+    <t>0.8225,0.0349,0.1538,0.0029</t>
+  </si>
+  <si>
+    <t>0.7020,0.0277,0.3142,0.0119</t>
+  </si>
+  <si>
+    <t>0.6179,0.0764,0.3727,0.0085</t>
+  </si>
+  <si>
+    <t>0.6827,0.1485,0.2486,0.0123</t>
+  </si>
+  <si>
+    <t>0.7003,0.0894,0.2426,0.0097</t>
+  </si>
+  <si>
+    <t>0.3844,0.1719,0.6290,0.0190</t>
+  </si>
+  <si>
+    <t>0.6321,0.1505,0.2679,0.0201</t>
+  </si>
+  <si>
+    <t>0.7857,0.0571,0.1003,0.0185</t>
+  </si>
+  <si>
+    <t>0.6701,0.0919,0.2831,0.0159</t>
+  </si>
+  <si>
+    <t>0.7608,0.0583,0.1382,0.0233</t>
+  </si>
+  <si>
+    <t>0.7384,0.0761,0.1691,0.0153</t>
+  </si>
+  <si>
+    <t>0.4977,0.2857,0.2047,0.0086</t>
+  </si>
+  <si>
+    <t>0.7046,0.0170,0.3650,0.0060</t>
+  </si>
+  <si>
+    <t>0.6620,0.0358,0.3970,0.0058</t>
+  </si>
+  <si>
+    <t>0.5764,0.0504,0.4618,0.0136</t>
+  </si>
+  <si>
+    <t>0.6877,0.0834,0.2791,0.0033</t>
+  </si>
+  <si>
+    <t>0.4181,0.3550,0.2637,0.0078</t>
+  </si>
+  <si>
+    <t>0.6769,0.0816,0.3030,0.0055</t>
+  </si>
+  <si>
+    <t>0.7636,0.0593,0.1548,0.0242</t>
+  </si>
+  <si>
+    <t>0.6441,0.2476,0.1792,0.0058</t>
+  </si>
+  <si>
+    <t>0.4029,0.4819,0.2521,0.0132</t>
+  </si>
+  <si>
+    <t>0.5768,0.2758,0.2685,0.0118</t>
+  </si>
+  <si>
+    <t>0.3369,0.1542,0.5536,0.0088</t>
+  </si>
+  <si>
+    <t>0.5858,0.0797,0.4166,0.0110</t>
+  </si>
+  <si>
+    <t>0.6453,0.0279,0.4657,0.0054</t>
+  </si>
+  <si>
+    <t>0.7561,0.0253,0.2531,0.0083</t>
+  </si>
+  <si>
+    <t>0.3215,0.0372,0.7688,0.0115</t>
+  </si>
+  <si>
+    <t>0.6240,0.0479,0.4226,0.0066</t>
+  </si>
+  <si>
+    <t>0.8096,0.0438,0.0961,0.0163</t>
+  </si>
+  <si>
+    <t>0.7617,0.0343,0.1293,0.0244</t>
+  </si>
+  <si>
+    <t>0.7021,0.0605,0.2039,0.0225</t>
+  </si>
+  <si>
+    <t>0.4354,0.1592,0.5819,0.0214</t>
+  </si>
+  <si>
+    <t>0.7315,0.0363,0.1288,0.0379</t>
+  </si>
+  <si>
+    <t>0.7025,0.0573,0.1082,0.0536</t>
+  </si>
+  <si>
+    <t>0.7401,0.0684,0.1099,0.0292</t>
+  </si>
+  <si>
+    <t>0.2226,0.6997,0.1062,0.0017</t>
+  </si>
+  <si>
+    <t>0.2528,0.1486,0.7178,0.0053</t>
+  </si>
+  <si>
+    <t>0.4808,0.0461,0.6304,0.0063</t>
+  </si>
+  <si>
+    <t>0.2899,0.2107,0.5816,0.0026</t>
+  </si>
+  <si>
+    <t>0.3802,0.0829,0.7011,0.0087</t>
+  </si>
+  <si>
+    <t>0.6851,0.2256,0.1202,0.0106</t>
+  </si>
+  <si>
+    <t>0.0142,0.9843,0.0307,0.0006</t>
+  </si>
+  <si>
+    <t>0.7521,0.0574,0.2000,0.0087</t>
+  </si>
+  <si>
+    <t>0.6991,0.0440,0.1263,0.0588</t>
+  </si>
+  <si>
+    <t>0.2878,0.2290,0.6286,0.0157</t>
+  </si>
+  <si>
+    <t>0.5398,0.1404,0.3908,0.0055</t>
+  </si>
+  <si>
+    <t>0.7100,0.1085,0.1713,0.0048</t>
+  </si>
+  <si>
+    <t>0.1497,0.8560,0.0299,0.0005</t>
+  </si>
+  <si>
+    <t>0.3475,0.3466,0.3274,0.0050</t>
+  </si>
+  <si>
+    <t>0.7390,0.0237,0.2003,0.0187</t>
+  </si>
+  <si>
+    <t>0.7294,0.0309,0.0890,0.0512</t>
+  </si>
+  <si>
+    <t>0.7694,0.0342,0.1168,0.0295</t>
+  </si>
+  <si>
+    <t>0.8211,0.0340,0.0898,0.0151</t>
+  </si>
+  <si>
+    <t>0.7123,0.0320,0.1736,0.0401</t>
+  </si>
+  <si>
+    <t>0.7790,0.0252,0.0494,0.0819</t>
+  </si>
+  <si>
+    <t>0.5452,0.2575,0.2079,0.0028</t>
+  </si>
+  <si>
+    <t>0.3035,0.3687,0.3469,0.0020</t>
+  </si>
+  <si>
+    <t>0.4525,0.3261,0.2607,0.0027</t>
+  </si>
+  <si>
+    <t>0.5264,0.1153,0.4249,0.0042</t>
+  </si>
+  <si>
+    <t>0.3492,0.5153,0.1630,0.0021</t>
+  </si>
+  <si>
+    <t>0.5786,0.1211,0.3118,0.0034</t>
+  </si>
+  <si>
+    <t>0.7562,0.0691,0.1305,0.0201</t>
+  </si>
+  <si>
+    <t>0.7705,0.0494,0.0972,0.0248</t>
+  </si>
+  <si>
+    <t>0.8218,0.0368,0.0914,0.0114</t>
+  </si>
+  <si>
+    <t>0.7115,0.0732,0.1232,0.0523</t>
+  </si>
+  <si>
+    <t>0.7333,0.0564,0.1348,0.0305</t>
+  </si>
+  <si>
+    <t>0.7209,0.0463,0.1233,0.0337</t>
+  </si>
+  <si>
+    <t>0.7101,0.0767,0.1460,0.0387</t>
+  </si>
+  <si>
+    <t>0.7502,0.0372,0.1241,0.0381</t>
+  </si>
+  <si>
+    <t>0.7154,0.0428,0.0870,0.0741</t>
+  </si>
+  <si>
+    <t>0.7679,0.0286,0.0795,0.0496</t>
+  </si>
+  <si>
+    <t>0.6732,0.0701,0.1199,0.0797</t>
+  </si>
+  <si>
+    <t>0.7401,0.0598,0.1152,0.0307</t>
+  </si>
+  <si>
+    <t>0.6869,0.0285,0.0992,0.0752</t>
+  </si>
+  <si>
+    <t>0.6704,0.1241,0.1472,0.0327</t>
+  </si>
+  <si>
+    <t>0.7194,0.0678,0.1462,0.0354</t>
+  </si>
+  <si>
+    <t>0.6816,0.0766,0.1576,0.0421</t>
+  </si>
+  <si>
+    <t>0.1991,0.0230,0.8839,0.0056</t>
+  </si>
+  <si>
+    <t>0.5785,0.0748,0.4618,0.0077</t>
+  </si>
+  <si>
+    <t>0.8742,0.0315,0.0708,0.0061</t>
+  </si>
+  <si>
+    <t>0.7781,0.0221,0.2345,0.0047</t>
+  </si>
+  <si>
+    <t>0.5473,0.3432,0.2298,0.0206</t>
+  </si>
+  <si>
+    <t>0.6852,0.1880,0.1607,0.0138</t>
+  </si>
+  <si>
+    <t>0.6082,0.2528,0.2310,0.0126</t>
+  </si>
+  <si>
+    <t>0.7324,0.0936,0.1871,0.0146</t>
+  </si>
+  <si>
+    <t>0.5311,0.3884,0.1859,0.0072</t>
+  </si>
+  <si>
+    <t>0.6045,0.2107,0.2624,0.0207</t>
+  </si>
+  <si>
+    <t>0.7532,0.0702,0.1976,0.0109</t>
+  </si>
+  <si>
+    <t>0.7761,0.0427,0.1680,0.0131</t>
+  </si>
+  <si>
+    <t>0.7064,0.0286,0.3229,0.0092</t>
+  </si>
+  <si>
+    <t>0.8075,0.0288,0.1777,0.0065</t>
+  </si>
+  <si>
+    <t>0.7403,0.0539,0.2054,0.0145</t>
+  </si>
+  <si>
+    <t>0.6886,0.0675,0.2257,0.0261</t>
+  </si>
+  <si>
+    <t>0.5767,0.4362,0.0918,0.0057</t>
+  </si>
+  <si>
+    <t>0.3742,0.6046,0.1540,0.0065</t>
+  </si>
+  <si>
+    <t>0.7308,0.0540,0.2003,0.0198</t>
+  </si>
+  <si>
+    <t>0.0829,0.8559,0.2471,0.0055</t>
+  </si>
+  <si>
+    <t>0.7615,0.0933,0.1134,0.0139</t>
+  </si>
+  <si>
+    <t>0.6936,0.0664,0.1829,0.0280</t>
+  </si>
+  <si>
+    <t>0.7185,0.0873,0.1881,0.0150</t>
+  </si>
+  <si>
+    <t>0.6977,0.0680,0.1642,0.0439</t>
+  </si>
+  <si>
+    <t>0.7146,0.0490,0.1942,0.0237</t>
+  </si>
+  <si>
+    <t>0.8400,0.0306,0.0611,0.0186</t>
+  </si>
+  <si>
+    <t>0.7298,0.0559,0.1863,0.0222</t>
+  </si>
+  <si>
+    <t>0.7117,0.0353,0.1243,0.0639</t>
+  </si>
+  <si>
+    <t>0.7027,0.0700,0.2122,0.0252</t>
+  </si>
+  <si>
+    <t>0.7561,0.0414,0.1290,0.0287</t>
+  </si>
+  <si>
+    <t>0.7278,0.0292,0.0928,0.0557</t>
+  </si>
+  <si>
+    <t>0.5876,0.0929,0.3948,0.0057</t>
+  </si>
+  <si>
+    <t>0.5366,0.0565,0.5287,0.0030</t>
+  </si>
+  <si>
+    <t>0.5043,0.0438,0.5590,0.0025</t>
+  </si>
+  <si>
+    <t>0.6848,0.0188,0.4408,0.0032</t>
+  </si>
+  <si>
+    <t>0.8144,0.0298,0.1862,0.0038</t>
+  </si>
+  <si>
+    <t>0.7636,0.0267,0.1930,0.0149</t>
+  </si>
+  <si>
+    <t>0.6750,0.0370,0.2980,0.0163</t>
+  </si>
+  <si>
+    <t>0.8029,0.0219,0.0671,0.0243</t>
+  </si>
+  <si>
+    <t>0.8312,0.0397,0.0868,0.0109</t>
+  </si>
+  <si>
+    <t>0.7826,0.0130,0.0879,0.0326</t>
+  </si>
+  <si>
+    <t>0.7429,0.0282,0.1375,0.0371</t>
+  </si>
+  <si>
+    <t>0.7433,0.0160,0.1555,0.0290</t>
+  </si>
+  <si>
+    <t>0.4630,0.2313,0.4160,0.0203</t>
+  </si>
+  <si>
+    <t>0.7127,0.0509,0.1519,0.0304</t>
+  </si>
+  <si>
+    <t>0.7288,0.0623,0.2062,0.0189</t>
+  </si>
+  <si>
+    <t>0.7573,0.0357,0.1454,0.0201</t>
+  </si>
+  <si>
+    <t>0.7259,0.0610,0.1621,0.0228</t>
+  </si>
+  <si>
+    <t>0.7595,0.0435,0.1377,0.0262</t>
+  </si>
+  <si>
+    <t>0.7283,0.0423,0.1539,0.0341</t>
+  </si>
+  <si>
+    <t>0.7153,0.0486,0.1512,0.0418</t>
+  </si>
+  <si>
+    <t>0.3175,0.1466,0.6861,0.0252</t>
+  </si>
+  <si>
+    <t>0.6097,0.0208,0.0813,0.1692</t>
+  </si>
+  <si>
+    <t>0.7182,0.0534,0.1755,0.0270</t>
+  </si>
+  <si>
+    <t>0.7201,0.0727,0.1553,0.0250</t>
+  </si>
+  <si>
+    <t>0.8092,0.0439,0.1020,0.0116</t>
+  </si>
+  <si>
+    <t>0.8467,0.0300,0.0947,0.0079</t>
+  </si>
+  <si>
+    <t>0.7325,0.0846,0.1628,0.0230</t>
+  </si>
+  <si>
+    <t>0.8343,0.0425,0.1330,0.0056</t>
+  </si>
+  <si>
+    <t>0.7133,0.0710,0.1789,0.0266</t>
+  </si>
+  <si>
+    <t>0.7344,0.0625,0.1512,0.0245</t>
+  </si>
+  <si>
+    <t>0.7281,0.0429,0.0959,0.0543</t>
+  </si>
+  <si>
+    <t>0.7122,0.0678,0.1541,0.0275</t>
+  </si>
+  <si>
+    <t>0.7887,0.0290,0.1250,0.0178</t>
+  </si>
+  <si>
+    <t>0.6492,0.0729,0.2658,0.0366</t>
+  </si>
+  <si>
+    <t>0.7517,0.0362,0.1274,0.0295</t>
+  </si>
+  <si>
+    <t>0.7614,0.0362,0.1396,0.0218</t>
+  </si>
+  <si>
+    <t>0.7341,0.0475,0.1148,0.0397</t>
+  </si>
+  <si>
+    <t>0.6726,0.1562,0.2343,0.0140</t>
+  </si>
+  <si>
+    <t>0.6440,0.1316,0.2345,0.0213</t>
+  </si>
+  <si>
+    <t>0.7910,0.0429,0.1266,0.0138</t>
+  </si>
+  <si>
+    <t>0.7515,0.0499,0.1527,0.0229</t>
+  </si>
+  <si>
+    <t>0.7553,0.0685,0.1086,0.0281</t>
+  </si>
+  <si>
+    <t>0.7656,0.0501,0.1007,0.0291</t>
+  </si>
+  <si>
+    <t>0.8185,0.0268,0.0893,0.0153</t>
+  </si>
+  <si>
+    <t>0.6630,0.0883,0.2366,0.0321</t>
+  </si>
+  <si>
+    <t>0.3920,0.1782,0.5452,0.0090</t>
+  </si>
+  <si>
+    <t>0.7079,0.0586,0.2011,0.0216</t>
+  </si>
+  <si>
+    <t>0.5921,0.0234,0.4595,0.0037</t>
+  </si>
+  <si>
+    <t>0.4255,0.3300,0.2613,0.0066</t>
+  </si>
+  <si>
+    <t>0.7381,0.0400,0.2667,0.0070</t>
+  </si>
+  <si>
+    <t>0.4444,0.1768,0.4342,0.0089</t>
+  </si>
+  <si>
+    <t>0.6421,0.0403,0.4447,0.0043</t>
+  </si>
+  <si>
+    <t>0.7327,0.0330,0.2922,0.0035</t>
+  </si>
+  <si>
+    <t>0.6047,0.0375,0.5003,0.0062</t>
+  </si>
+  <si>
+    <t>0.7525,0.0989,0.1706,0.0063</t>
+  </si>
+  <si>
+    <t>0.6912,0.0913,0.2611,0.0088</t>
+  </si>
+  <si>
+    <t>0.7393,0.0502,0.2663,0.0071</t>
+  </si>
+  <si>
+    <t>0.6232,0.1358,0.3090,0.0104</t>
+  </si>
+  <si>
+    <t>0.7324,0.1282,0.1780,0.0068</t>
+  </si>
+  <si>
+    <t>0.8398,0.0234,0.1137,0.0091</t>
+  </si>
+  <si>
+    <t>0.7970,0.0482,0.1737,0.0127</t>
+  </si>
+  <si>
+    <t>0.7096,0.0821,0.2595,0.0083</t>
+  </si>
+  <si>
+    <t>0.7503,0.0596,0.1037,0.0351</t>
+  </si>
+  <si>
+    <t>0.6273,0.1716,0.2522,0.0272</t>
+  </si>
+  <si>
+    <t>0.6907,0.1209,0.2246,0.0161</t>
+  </si>
+  <si>
+    <t>0.7629,0.0454,0.1240,0.0235</t>
+  </si>
+  <si>
+    <t>0.7042,0.0697,0.1525,0.0362</t>
+  </si>
+  <si>
+    <t>0.7832,0.0730,0.1651,0.0068</t>
+  </si>
+  <si>
+    <t>0.7604,0.0535,0.2272,0.0061</t>
+  </si>
+  <si>
+    <t>0.7822,0.0406,0.1895,0.0068</t>
+  </si>
+  <si>
+    <t>0.8102,0.0409,0.1304,0.0091</t>
+  </si>
+  <si>
+    <t>0.7793,0.0187,0.1913,0.0103</t>
+  </si>
+  <si>
+    <t>0.6125,0.0249,0.4061,0.0161</t>
+  </si>
+  <si>
+    <t>0.7171,0.0537,0.2382,0.0089</t>
+  </si>
+  <si>
+    <t>0.6628,0.0760,0.3031,0.0055</t>
+  </si>
+  <si>
+    <t>0.6899,0.0478,0.3124,0.0098</t>
+  </si>
+  <si>
+    <t>0.6730,0.0441,0.3378,0.0033</t>
+  </si>
+  <si>
+    <t>0.7814,0.0433,0.0878,0.0332</t>
+  </si>
+  <si>
+    <t>0.7592,0.0612,0.1205,0.0233</t>
+  </si>
+  <si>
+    <t>0.7155,0.0677,0.1483,0.0273</t>
+  </si>
+  <si>
+    <t>0.6872,0.0927,0.1459,0.0504</t>
+  </si>
+  <si>
+    <t>0.5956,0.1159,0.2535,0.0529</t>
+  </si>
+  <si>
+    <t>0.7022,0.0843,0.1592,0.0329</t>
+  </si>
+  <si>
+    <t>0.7306,0.0707,0.1479,0.0209</t>
+  </si>
+  <si>
+    <t>0.7442,0.0454,0.1290,0.0320</t>
+  </si>
+  <si>
+    <t>0.7384,0.0248,0.2425,0.0118</t>
+  </si>
+  <si>
+    <t>0.7946,0.0355,0.1063,0.0223</t>
+  </si>
+  <si>
+    <t>0.7457,0.0526,0.2018,0.0115</t>
+  </si>
+  <si>
+    <t>0.7047,0.0466,0.3125,0.0046</t>
+  </si>
+  <si>
+    <t>0.4662,0.0548,0.5978,0.0098</t>
+  </si>
+  <si>
+    <t>0.5921,0.0534,0.4564,0.0036</t>
+  </si>
+  <si>
+    <t>0.3574,0.0323,0.7506,0.0073</t>
+  </si>
+  <si>
+    <t>0.7245,0.0665,0.2624,0.0063</t>
+  </si>
+  <si>
+    <t>0.3739,0.0441,0.6735,0.0148</t>
+  </si>
+  <si>
+    <t>0.5555,0.0401,0.5197,0.0043</t>
+  </si>
+  <si>
+    <t>0.7763,0.0472,0.1576,0.0131</t>
+  </si>
+  <si>
+    <t>0.7948,0.0231,0.2030,0.0059</t>
+  </si>
+  <si>
+    <t>0.7156,0.0457,0.2575,0.0152</t>
+  </si>
+  <si>
+    <t>0.7766,0.0434,0.2103,0.0068</t>
+  </si>
+  <si>
+    <t>0.6807,0.0500,0.1530,0.0504</t>
+  </si>
+  <si>
+    <t>0.6966,0.0725,0.2243,0.0157</t>
+  </si>
+  <si>
+    <t>0.6912,0.0586,0.1273,0.0552</t>
+  </si>
+  <si>
+    <t>0.7381,0.0526,0.1172,0.0357</t>
+  </si>
+  <si>
+    <t>0.6711,0.0916,0.1573,0.0426</t>
+  </si>
+  <si>
+    <t>0.7293,0.0593,0.1059,0.0419</t>
+  </si>
+  <si>
+    <t>0.7196,0.0699,0.1760,0.0254</t>
+  </si>
+  <si>
+    <t>0.6795,0.0813,0.1539,0.0370</t>
+  </si>
+  <si>
+    <t>0.4461,0.0624,0.6418,0.0068</t>
+  </si>
+  <si>
+    <t>0.4991,0.0437,0.5718,0.0049</t>
+  </si>
+  <si>
+    <t>0.4432,0.0675,0.5880,0.0109</t>
+  </si>
+  <si>
+    <t>0.6886,0.0480,0.3398,0.0078</t>
+  </si>
+  <si>
+    <t>0.5245,0.0673,0.5270,0.0118</t>
+  </si>
+  <si>
+    <t>0.7904,0.0271,0.1935,0.0077</t>
+  </si>
+  <si>
+    <t>0.8061,0.0130,0.2262,0.0024</t>
+  </si>
+  <si>
+    <t>0.7834,0.0375,0.1645,0.0101</t>
+  </si>
+  <si>
+    <t>0.7087,0.0625,0.1791,0.0265</t>
+  </si>
+  <si>
+    <t>0.7181,0.0493,0.1792,0.0266</t>
+  </si>
+  <si>
+    <t>0.7801,0.0274,0.1223,0.0262</t>
+  </si>
+  <si>
+    <t>0.7511,0.0301,0.1389,0.0259</t>
+  </si>
+  <si>
+    <t>0.7964,0.0294,0.0946,0.0266</t>
+  </si>
+  <si>
+    <t>0.7818,0.0377,0.1430,0.0175</t>
   </si>
 </sst>
 </file>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2639,7 +2639,7 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D51" t="s">
         <v>313</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>

--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.7911,0.0293,0.1256,0.0199</t>
-  </si>
-  <si>
-    <t>0.7955,0.0285,0.1154,0.0158</t>
-  </si>
-  <si>
-    <t>0.7753,0.0294,0.1052,0.0256</t>
-  </si>
-  <si>
-    <t>0.8254,0.0255,0.1008,0.0122</t>
-  </si>
-  <si>
-    <t>0.7256,0.0378,0.1133,0.0555</t>
-  </si>
-  <si>
-    <t>0.7164,0.0760,0.0981,0.0421</t>
-  </si>
-  <si>
-    <t>0.7456,0.0584,0.1137,0.0284</t>
-  </si>
-  <si>
-    <t>0.6316,0.0479,0.1361,0.0971</t>
-  </si>
-  <si>
-    <t>0.7005,0.1020,0.1218,0.0405</t>
-  </si>
-  <si>
-    <t>0.7108,0.0706,0.1164,0.0435</t>
-  </si>
-  <si>
-    <t>0.7015,0.0655,0.1868,0.0268</t>
-  </si>
-  <si>
-    <t>0.6870,0.0548,0.0882,0.0780</t>
-  </si>
-  <si>
-    <t>0.6981,0.0599,0.2481,0.0155</t>
-  </si>
-  <si>
-    <t>0.7329,0.0609,0.2582,0.0067</t>
-  </si>
-  <si>
-    <t>0.7850,0.0384,0.2262,0.0028</t>
-  </si>
-  <si>
-    <t>0.8110,0.0310,0.2173,0.0036</t>
-  </si>
-  <si>
-    <t>0.6192,0.1757,0.2998,0.0157</t>
-  </si>
-  <si>
-    <t>0.7195,0.1228,0.1501,0.0173</t>
-  </si>
-  <si>
-    <t>0.5824,0.3219,0.1767,0.0058</t>
-  </si>
-  <si>
-    <t>0.6702,0.1372,0.2206,0.0153</t>
-  </si>
-  <si>
-    <t>0.5635,0.3093,0.2282,0.0153</t>
-  </si>
-  <si>
-    <t>0.4192,0.4779,0.2573,0.0110</t>
-  </si>
-  <si>
-    <t>0.7929,0.0242,0.2083,0.0080</t>
-  </si>
-  <si>
-    <t>0.8464,0.0199,0.1366,0.0033</t>
-  </si>
-  <si>
-    <t>0.7289,0.0271,0.3129,0.0063</t>
-  </si>
-  <si>
-    <t>0.7582,0.0370,0.2378,0.0058</t>
-  </si>
-  <si>
-    <t>0.8225,0.0349,0.1538,0.0029</t>
-  </si>
-  <si>
-    <t>0.7020,0.0277,0.3142,0.0119</t>
-  </si>
-  <si>
-    <t>0.6179,0.0764,0.3727,0.0085</t>
-  </si>
-  <si>
-    <t>0.6827,0.1485,0.2486,0.0123</t>
-  </si>
-  <si>
-    <t>0.7003,0.0894,0.2426,0.0097</t>
-  </si>
-  <si>
-    <t>0.3844,0.1719,0.6290,0.0190</t>
-  </si>
-  <si>
-    <t>0.6321,0.1505,0.2679,0.0201</t>
-  </si>
-  <si>
-    <t>0.7857,0.0571,0.1003,0.0185</t>
-  </si>
-  <si>
-    <t>0.6701,0.0919,0.2831,0.0159</t>
-  </si>
-  <si>
-    <t>0.7608,0.0583,0.1382,0.0233</t>
-  </si>
-  <si>
-    <t>0.7384,0.0761,0.1691,0.0153</t>
-  </si>
-  <si>
-    <t>0.4977,0.2857,0.2047,0.0086</t>
-  </si>
-  <si>
-    <t>0.7046,0.0170,0.3650,0.0060</t>
-  </si>
-  <si>
-    <t>0.6620,0.0358,0.3970,0.0058</t>
-  </si>
-  <si>
-    <t>0.5764,0.0504,0.4618,0.0136</t>
-  </si>
-  <si>
-    <t>0.6877,0.0834,0.2791,0.0033</t>
-  </si>
-  <si>
-    <t>0.4181,0.3550,0.2637,0.0078</t>
-  </si>
-  <si>
-    <t>0.6769,0.0816,0.3030,0.0055</t>
-  </si>
-  <si>
-    <t>0.7636,0.0593,0.1548,0.0242</t>
-  </si>
-  <si>
-    <t>0.6441,0.2476,0.1792,0.0058</t>
-  </si>
-  <si>
-    <t>0.4029,0.4819,0.2521,0.0132</t>
-  </si>
-  <si>
-    <t>0.5768,0.2758,0.2685,0.0118</t>
-  </si>
-  <si>
-    <t>0.3369,0.1542,0.5536,0.0088</t>
-  </si>
-  <si>
-    <t>0.5858,0.0797,0.4166,0.0110</t>
-  </si>
-  <si>
-    <t>0.6453,0.0279,0.4657,0.0054</t>
-  </si>
-  <si>
-    <t>0.7561,0.0253,0.2531,0.0083</t>
-  </si>
-  <si>
-    <t>0.3215,0.0372,0.7688,0.0115</t>
-  </si>
-  <si>
-    <t>0.6240,0.0479,0.4226,0.0066</t>
-  </si>
-  <si>
-    <t>0.8096,0.0438,0.0961,0.0163</t>
-  </si>
-  <si>
-    <t>0.7617,0.0343,0.1293,0.0244</t>
-  </si>
-  <si>
-    <t>0.7021,0.0605,0.2039,0.0225</t>
-  </si>
-  <si>
-    <t>0.4354,0.1592,0.5819,0.0214</t>
-  </si>
-  <si>
-    <t>0.7315,0.0363,0.1288,0.0379</t>
-  </si>
-  <si>
-    <t>0.7025,0.0573,0.1082,0.0536</t>
-  </si>
-  <si>
-    <t>0.7401,0.0684,0.1099,0.0292</t>
-  </si>
-  <si>
-    <t>0.2226,0.6997,0.1062,0.0017</t>
-  </si>
-  <si>
-    <t>0.2528,0.1486,0.7178,0.0053</t>
-  </si>
-  <si>
-    <t>0.4808,0.0461,0.6304,0.0063</t>
-  </si>
-  <si>
-    <t>0.2899,0.2107,0.5816,0.0026</t>
-  </si>
-  <si>
-    <t>0.3802,0.0829,0.7011,0.0087</t>
-  </si>
-  <si>
-    <t>0.6851,0.2256,0.1202,0.0106</t>
-  </si>
-  <si>
-    <t>0.0142,0.9843,0.0307,0.0006</t>
-  </si>
-  <si>
-    <t>0.7521,0.0574,0.2000,0.0087</t>
-  </si>
-  <si>
-    <t>0.6991,0.0440,0.1263,0.0588</t>
-  </si>
-  <si>
-    <t>0.2878,0.2290,0.6286,0.0157</t>
-  </si>
-  <si>
-    <t>0.5398,0.1404,0.3908,0.0055</t>
-  </si>
-  <si>
-    <t>0.7100,0.1085,0.1713,0.0048</t>
-  </si>
-  <si>
-    <t>0.1497,0.8560,0.0299,0.0005</t>
-  </si>
-  <si>
-    <t>0.3475,0.3466,0.3274,0.0050</t>
-  </si>
-  <si>
-    <t>0.7390,0.0237,0.2003,0.0187</t>
-  </si>
-  <si>
-    <t>0.7294,0.0309,0.0890,0.0512</t>
-  </si>
-  <si>
-    <t>0.7694,0.0342,0.1168,0.0295</t>
-  </si>
-  <si>
-    <t>0.8211,0.0340,0.0898,0.0151</t>
-  </si>
-  <si>
-    <t>0.7123,0.0320,0.1736,0.0401</t>
-  </si>
-  <si>
-    <t>0.7790,0.0252,0.0494,0.0819</t>
-  </si>
-  <si>
-    <t>0.5452,0.2575,0.2079,0.0028</t>
-  </si>
-  <si>
-    <t>0.3035,0.3687,0.3469,0.0020</t>
-  </si>
-  <si>
-    <t>0.4525,0.3261,0.2607,0.0027</t>
-  </si>
-  <si>
-    <t>0.5264,0.1153,0.4249,0.0042</t>
-  </si>
-  <si>
-    <t>0.3492,0.5153,0.1630,0.0021</t>
-  </si>
-  <si>
-    <t>0.5786,0.1211,0.3118,0.0034</t>
-  </si>
-  <si>
-    <t>0.7562,0.0691,0.1305,0.0201</t>
-  </si>
-  <si>
-    <t>0.7705,0.0494,0.0972,0.0248</t>
-  </si>
-  <si>
-    <t>0.8218,0.0368,0.0914,0.0114</t>
-  </si>
-  <si>
-    <t>0.7115,0.0732,0.1232,0.0523</t>
-  </si>
-  <si>
-    <t>0.7333,0.0564,0.1348,0.0305</t>
-  </si>
-  <si>
-    <t>0.7209,0.0463,0.1233,0.0337</t>
-  </si>
-  <si>
-    <t>0.7101,0.0767,0.1460,0.0387</t>
-  </si>
-  <si>
-    <t>0.7502,0.0372,0.1241,0.0381</t>
-  </si>
-  <si>
-    <t>0.7154,0.0428,0.0870,0.0741</t>
-  </si>
-  <si>
-    <t>0.7679,0.0286,0.0795,0.0496</t>
-  </si>
-  <si>
-    <t>0.6732,0.0701,0.1199,0.0797</t>
-  </si>
-  <si>
-    <t>0.7401,0.0598,0.1152,0.0307</t>
-  </si>
-  <si>
-    <t>0.6869,0.0285,0.0992,0.0752</t>
-  </si>
-  <si>
-    <t>0.6704,0.1241,0.1472,0.0327</t>
-  </si>
-  <si>
-    <t>0.7194,0.0678,0.1462,0.0354</t>
-  </si>
-  <si>
-    <t>0.6816,0.0766,0.1576,0.0421</t>
-  </si>
-  <si>
-    <t>0.1991,0.0230,0.8839,0.0056</t>
-  </si>
-  <si>
-    <t>0.5785,0.0748,0.4618,0.0077</t>
-  </si>
-  <si>
-    <t>0.8742,0.0315,0.0708,0.0061</t>
-  </si>
-  <si>
-    <t>0.7781,0.0221,0.2345,0.0047</t>
-  </si>
-  <si>
-    <t>0.5473,0.3432,0.2298,0.0206</t>
-  </si>
-  <si>
-    <t>0.6852,0.1880,0.1607,0.0138</t>
-  </si>
-  <si>
-    <t>0.6082,0.2528,0.2310,0.0126</t>
-  </si>
-  <si>
-    <t>0.7324,0.0936,0.1871,0.0146</t>
-  </si>
-  <si>
-    <t>0.5311,0.3884,0.1859,0.0072</t>
-  </si>
-  <si>
-    <t>0.6045,0.2107,0.2624,0.0207</t>
-  </si>
-  <si>
-    <t>0.7532,0.0702,0.1976,0.0109</t>
-  </si>
-  <si>
-    <t>0.7761,0.0427,0.1680,0.0131</t>
-  </si>
-  <si>
-    <t>0.7064,0.0286,0.3229,0.0092</t>
-  </si>
-  <si>
-    <t>0.8075,0.0288,0.1777,0.0065</t>
-  </si>
-  <si>
-    <t>0.7403,0.0539,0.2054,0.0145</t>
-  </si>
-  <si>
-    <t>0.6886,0.0675,0.2257,0.0261</t>
-  </si>
-  <si>
-    <t>0.5767,0.4362,0.0918,0.0057</t>
-  </si>
-  <si>
-    <t>0.3742,0.6046,0.1540,0.0065</t>
-  </si>
-  <si>
-    <t>0.7308,0.0540,0.2003,0.0198</t>
-  </si>
-  <si>
-    <t>0.0829,0.8559,0.2471,0.0055</t>
-  </si>
-  <si>
-    <t>0.7615,0.0933,0.1134,0.0139</t>
-  </si>
-  <si>
-    <t>0.6936,0.0664,0.1829,0.0280</t>
-  </si>
-  <si>
-    <t>0.7185,0.0873,0.1881,0.0150</t>
-  </si>
-  <si>
-    <t>0.6977,0.0680,0.1642,0.0439</t>
-  </si>
-  <si>
-    <t>0.7146,0.0490,0.1942,0.0237</t>
-  </si>
-  <si>
-    <t>0.8400,0.0306,0.0611,0.0186</t>
-  </si>
-  <si>
-    <t>0.7298,0.0559,0.1863,0.0222</t>
-  </si>
-  <si>
-    <t>0.7117,0.0353,0.1243,0.0639</t>
-  </si>
-  <si>
-    <t>0.7027,0.0700,0.2122,0.0252</t>
-  </si>
-  <si>
-    <t>0.7561,0.0414,0.1290,0.0287</t>
-  </si>
-  <si>
-    <t>0.7278,0.0292,0.0928,0.0557</t>
-  </si>
-  <si>
-    <t>0.5876,0.0929,0.3948,0.0057</t>
-  </si>
-  <si>
-    <t>0.5366,0.0565,0.5287,0.0030</t>
-  </si>
-  <si>
-    <t>0.5043,0.0438,0.5590,0.0025</t>
-  </si>
-  <si>
-    <t>0.6848,0.0188,0.4408,0.0032</t>
-  </si>
-  <si>
-    <t>0.8144,0.0298,0.1862,0.0038</t>
-  </si>
-  <si>
-    <t>0.7636,0.0267,0.1930,0.0149</t>
-  </si>
-  <si>
-    <t>0.6750,0.0370,0.2980,0.0163</t>
-  </si>
-  <si>
-    <t>0.8029,0.0219,0.0671,0.0243</t>
-  </si>
-  <si>
-    <t>0.8312,0.0397,0.0868,0.0109</t>
-  </si>
-  <si>
-    <t>0.7826,0.0130,0.0879,0.0326</t>
-  </si>
-  <si>
-    <t>0.7429,0.0282,0.1375,0.0371</t>
-  </si>
-  <si>
-    <t>0.7433,0.0160,0.1555,0.0290</t>
-  </si>
-  <si>
-    <t>0.4630,0.2313,0.4160,0.0203</t>
-  </si>
-  <si>
-    <t>0.7127,0.0509,0.1519,0.0304</t>
-  </si>
-  <si>
-    <t>0.7288,0.0623,0.2062,0.0189</t>
-  </si>
-  <si>
-    <t>0.7573,0.0357,0.1454,0.0201</t>
-  </si>
-  <si>
-    <t>0.7259,0.0610,0.1621,0.0228</t>
-  </si>
-  <si>
-    <t>0.7595,0.0435,0.1377,0.0262</t>
-  </si>
-  <si>
-    <t>0.7283,0.0423,0.1539,0.0341</t>
-  </si>
-  <si>
-    <t>0.7153,0.0486,0.1512,0.0418</t>
-  </si>
-  <si>
-    <t>0.3175,0.1466,0.6861,0.0252</t>
-  </si>
-  <si>
-    <t>0.6097,0.0208,0.0813,0.1692</t>
-  </si>
-  <si>
-    <t>0.7182,0.0534,0.1755,0.0270</t>
-  </si>
-  <si>
-    <t>0.7201,0.0727,0.1553,0.0250</t>
-  </si>
-  <si>
-    <t>0.8092,0.0439,0.1020,0.0116</t>
-  </si>
-  <si>
-    <t>0.8467,0.0300,0.0947,0.0079</t>
-  </si>
-  <si>
-    <t>0.7325,0.0846,0.1628,0.0230</t>
-  </si>
-  <si>
-    <t>0.8343,0.0425,0.1330,0.0056</t>
-  </si>
-  <si>
-    <t>0.7133,0.0710,0.1789,0.0266</t>
-  </si>
-  <si>
-    <t>0.7344,0.0625,0.1512,0.0245</t>
-  </si>
-  <si>
-    <t>0.7281,0.0429,0.0959,0.0543</t>
-  </si>
-  <si>
-    <t>0.7122,0.0678,0.1541,0.0275</t>
-  </si>
-  <si>
-    <t>0.7887,0.0290,0.1250,0.0178</t>
-  </si>
-  <si>
-    <t>0.6492,0.0729,0.2658,0.0366</t>
-  </si>
-  <si>
-    <t>0.7517,0.0362,0.1274,0.0295</t>
-  </si>
-  <si>
-    <t>0.7614,0.0362,0.1396,0.0218</t>
-  </si>
-  <si>
-    <t>0.7341,0.0475,0.1148,0.0397</t>
-  </si>
-  <si>
-    <t>0.6726,0.1562,0.2343,0.0140</t>
-  </si>
-  <si>
-    <t>0.6440,0.1316,0.2345,0.0213</t>
-  </si>
-  <si>
-    <t>0.7910,0.0429,0.1266,0.0138</t>
-  </si>
-  <si>
-    <t>0.7515,0.0499,0.1527,0.0229</t>
-  </si>
-  <si>
-    <t>0.7553,0.0685,0.1086,0.0281</t>
-  </si>
-  <si>
-    <t>0.7656,0.0501,0.1007,0.0291</t>
-  </si>
-  <si>
-    <t>0.8185,0.0268,0.0893,0.0153</t>
-  </si>
-  <si>
-    <t>0.6630,0.0883,0.2366,0.0321</t>
-  </si>
-  <si>
-    <t>0.3920,0.1782,0.5452,0.0090</t>
-  </si>
-  <si>
-    <t>0.7079,0.0586,0.2011,0.0216</t>
-  </si>
-  <si>
-    <t>0.5921,0.0234,0.4595,0.0037</t>
-  </si>
-  <si>
-    <t>0.4255,0.3300,0.2613,0.0066</t>
-  </si>
-  <si>
-    <t>0.7381,0.0400,0.2667,0.0070</t>
-  </si>
-  <si>
-    <t>0.4444,0.1768,0.4342,0.0089</t>
-  </si>
-  <si>
-    <t>0.6421,0.0403,0.4447,0.0043</t>
-  </si>
-  <si>
-    <t>0.7327,0.0330,0.2922,0.0035</t>
-  </si>
-  <si>
-    <t>0.6047,0.0375,0.5003,0.0062</t>
-  </si>
-  <si>
-    <t>0.7525,0.0989,0.1706,0.0063</t>
-  </si>
-  <si>
-    <t>0.6912,0.0913,0.2611,0.0088</t>
-  </si>
-  <si>
-    <t>0.7393,0.0502,0.2663,0.0071</t>
-  </si>
-  <si>
-    <t>0.6232,0.1358,0.3090,0.0104</t>
-  </si>
-  <si>
-    <t>0.7324,0.1282,0.1780,0.0068</t>
-  </si>
-  <si>
-    <t>0.8398,0.0234,0.1137,0.0091</t>
-  </si>
-  <si>
-    <t>0.7970,0.0482,0.1737,0.0127</t>
-  </si>
-  <si>
-    <t>0.7096,0.0821,0.2595,0.0083</t>
-  </si>
-  <si>
-    <t>0.7503,0.0596,0.1037,0.0351</t>
-  </si>
-  <si>
-    <t>0.6273,0.1716,0.2522,0.0272</t>
-  </si>
-  <si>
-    <t>0.6907,0.1209,0.2246,0.0161</t>
-  </si>
-  <si>
-    <t>0.7629,0.0454,0.1240,0.0235</t>
-  </si>
-  <si>
-    <t>0.7042,0.0697,0.1525,0.0362</t>
-  </si>
-  <si>
-    <t>0.7832,0.0730,0.1651,0.0068</t>
-  </si>
-  <si>
-    <t>0.7604,0.0535,0.2272,0.0061</t>
-  </si>
-  <si>
-    <t>0.7822,0.0406,0.1895,0.0068</t>
-  </si>
-  <si>
-    <t>0.8102,0.0409,0.1304,0.0091</t>
-  </si>
-  <si>
-    <t>0.7793,0.0187,0.1913,0.0103</t>
-  </si>
-  <si>
-    <t>0.6125,0.0249,0.4061,0.0161</t>
-  </si>
-  <si>
-    <t>0.7171,0.0537,0.2382,0.0089</t>
-  </si>
-  <si>
-    <t>0.6628,0.0760,0.3031,0.0055</t>
-  </si>
-  <si>
-    <t>0.6899,0.0478,0.3124,0.0098</t>
-  </si>
-  <si>
-    <t>0.6730,0.0441,0.3378,0.0033</t>
-  </si>
-  <si>
-    <t>0.7814,0.0433,0.0878,0.0332</t>
-  </si>
-  <si>
-    <t>0.7592,0.0612,0.1205,0.0233</t>
-  </si>
-  <si>
-    <t>0.7155,0.0677,0.1483,0.0273</t>
-  </si>
-  <si>
-    <t>0.6872,0.0927,0.1459,0.0504</t>
-  </si>
-  <si>
-    <t>0.5956,0.1159,0.2535,0.0529</t>
-  </si>
-  <si>
-    <t>0.7022,0.0843,0.1592,0.0329</t>
-  </si>
-  <si>
-    <t>0.7306,0.0707,0.1479,0.0209</t>
-  </si>
-  <si>
-    <t>0.7442,0.0454,0.1290,0.0320</t>
-  </si>
-  <si>
-    <t>0.7384,0.0248,0.2425,0.0118</t>
-  </si>
-  <si>
-    <t>0.7946,0.0355,0.1063,0.0223</t>
-  </si>
-  <si>
-    <t>0.7457,0.0526,0.2018,0.0115</t>
-  </si>
-  <si>
-    <t>0.7047,0.0466,0.3125,0.0046</t>
-  </si>
-  <si>
-    <t>0.4662,0.0548,0.5978,0.0098</t>
-  </si>
-  <si>
-    <t>0.5921,0.0534,0.4564,0.0036</t>
-  </si>
-  <si>
-    <t>0.3574,0.0323,0.7506,0.0073</t>
-  </si>
-  <si>
-    <t>0.7245,0.0665,0.2624,0.0063</t>
-  </si>
-  <si>
-    <t>0.3739,0.0441,0.6735,0.0148</t>
-  </si>
-  <si>
-    <t>0.5555,0.0401,0.5197,0.0043</t>
-  </si>
-  <si>
-    <t>0.7763,0.0472,0.1576,0.0131</t>
-  </si>
-  <si>
-    <t>0.7948,0.0231,0.2030,0.0059</t>
-  </si>
-  <si>
-    <t>0.7156,0.0457,0.2575,0.0152</t>
-  </si>
-  <si>
-    <t>0.7766,0.0434,0.2103,0.0068</t>
-  </si>
-  <si>
-    <t>0.6807,0.0500,0.1530,0.0504</t>
-  </si>
-  <si>
-    <t>0.6966,0.0725,0.2243,0.0157</t>
-  </si>
-  <si>
-    <t>0.6912,0.0586,0.1273,0.0552</t>
-  </si>
-  <si>
-    <t>0.7381,0.0526,0.1172,0.0357</t>
-  </si>
-  <si>
-    <t>0.6711,0.0916,0.1573,0.0426</t>
-  </si>
-  <si>
-    <t>0.7293,0.0593,0.1059,0.0419</t>
-  </si>
-  <si>
-    <t>0.7196,0.0699,0.1760,0.0254</t>
-  </si>
-  <si>
-    <t>0.6795,0.0813,0.1539,0.0370</t>
-  </si>
-  <si>
-    <t>0.4461,0.0624,0.6418,0.0068</t>
-  </si>
-  <si>
-    <t>0.4991,0.0437,0.5718,0.0049</t>
-  </si>
-  <si>
-    <t>0.4432,0.0675,0.5880,0.0109</t>
-  </si>
-  <si>
-    <t>0.6886,0.0480,0.3398,0.0078</t>
-  </si>
-  <si>
-    <t>0.5245,0.0673,0.5270,0.0118</t>
-  </si>
-  <si>
-    <t>0.7904,0.0271,0.1935,0.0077</t>
-  </si>
-  <si>
-    <t>0.8061,0.0130,0.2262,0.0024</t>
-  </si>
-  <si>
-    <t>0.7834,0.0375,0.1645,0.0101</t>
-  </si>
-  <si>
-    <t>0.7087,0.0625,0.1791,0.0265</t>
-  </si>
-  <si>
-    <t>0.7181,0.0493,0.1792,0.0266</t>
-  </si>
-  <si>
-    <t>0.7801,0.0274,0.1223,0.0262</t>
-  </si>
-  <si>
-    <t>0.7511,0.0301,0.1389,0.0259</t>
-  </si>
-  <si>
-    <t>0.7964,0.0294,0.0946,0.0266</t>
-  </si>
-  <si>
-    <t>0.7818,0.0377,0.1430,0.0175</t>
+    <t>0.9293,0.0182,0.0206,0.0206</t>
+  </si>
+  <si>
+    <t>0.0030,0.0013,0.0003,0.9982</t>
+  </si>
+  <si>
+    <t>0.9560,0.0093,0.0101,0.0126</t>
+  </si>
+  <si>
+    <t>0.0730,0.0027,0.0167,0.9463</t>
+  </si>
+  <si>
+    <t>0.9850,0.0027,0.0048,0.0022</t>
+  </si>
+  <si>
+    <t>0.9781,0.0025,0.0009,0.0092</t>
+  </si>
+  <si>
+    <t>0.9847,0.0032,0.0025,0.0037</t>
+  </si>
+  <si>
+    <t>0.9797,0.0012,0.0008,0.0134</t>
+  </si>
+  <si>
+    <t>0.9793,0.0041,0.0017,0.0057</t>
+  </si>
+  <si>
+    <t>0.9845,0.0021,0.0009,0.0057</t>
+  </si>
+  <si>
+    <t>0.9662,0.0038,0.0021,0.0161</t>
+  </si>
+  <si>
+    <t>0.9877,0.0029,0.0013,0.0029</t>
+  </si>
+  <si>
+    <t>0.6791,0.0469,0.2914,0.0159</t>
+  </si>
+  <si>
+    <t>0.3109,0.0469,0.7176,0.0216</t>
+  </si>
+  <si>
+    <t>0.4381,0.0146,0.7242,0.0071</t>
+  </si>
+  <si>
+    <t>0.0672,0.0631,0.8809,0.0105</t>
+  </si>
+  <si>
+    <t>0.2991,0.0261,0.7758,0.0131</t>
+  </si>
+  <si>
+    <t>0.0112,0.9854,0.0092,0.0005</t>
+  </si>
+  <si>
+    <t>0.0051,0.9927,0.0063,0.0005</t>
+  </si>
+  <si>
+    <t>0.2596,0.7606,0.0287,0.0033</t>
+  </si>
+  <si>
+    <t>0.0018,0.9966,0.0023,0.0004</t>
+  </si>
+  <si>
+    <t>0.0007,0.9986,0.0019,0.0001</t>
+  </si>
+  <si>
+    <t>0.3820,0.0150,0.4950,0.1133</t>
+  </si>
+  <si>
+    <t>0.3677,0.1128,0.5283,0.0714</t>
+  </si>
+  <si>
+    <t>0.0019,0.0004,0.9964,0.0029</t>
+  </si>
+  <si>
+    <t>0.2072,0.0422,0.7945,0.0473</t>
+  </si>
+  <si>
+    <t>0.2574,0.0082,0.8750,0.0055</t>
+  </si>
+  <si>
+    <t>0.0185,0.0017,0.9886,0.0035</t>
+  </si>
+  <si>
+    <t>0.0038,0.0009,0.9945,0.0031</t>
+  </si>
+  <si>
+    <t>0.0848,0.9207,0.0137,0.0159</t>
+  </si>
+  <si>
+    <t>0.4445,0.0871,0.5881,0.0184</t>
+  </si>
+  <si>
+    <t>0.0126,0.0039,0.9901,0.0047</t>
+  </si>
+  <si>
+    <t>0.0125,0.9602,0.0771,0.0022</t>
+  </si>
+  <si>
+    <t>0.8106,0.0322,0.1332,0.0295</t>
+  </si>
+  <si>
+    <t>0.7115,0.0300,0.2710,0.0153</t>
+  </si>
+  <si>
+    <t>0.6010,0.3657,0.1037,0.0196</t>
+  </si>
+  <si>
+    <t>0.0482,0.8840,0.4279,0.0096</t>
+  </si>
+  <si>
+    <t>0.1150,0.5434,0.5804,0.0653</t>
+  </si>
+  <si>
+    <t>0.0266,0.0043,0.9294,0.0510</t>
+  </si>
+  <si>
+    <t>0.0711,0.0411,0.9187,0.0196</t>
+  </si>
+  <si>
+    <t>0.0313,0.0035,0.9580,0.0256</t>
+  </si>
+  <si>
+    <t>0.0535,0.0509,0.9270,0.0154</t>
+  </si>
+  <si>
+    <t>0.0138,0.9824,0.0035,0.0011</t>
+  </si>
+  <si>
+    <t>0.0451,0.0686,0.9054,0.0163</t>
+  </si>
+  <si>
+    <t>0.6559,0.1259,0.0246,0.2740</t>
+  </si>
+  <si>
+    <t>0.0006,0.9927,0.0029,0.0277</t>
+  </si>
+  <si>
+    <t>0.0015,0.9941,0.0273,0.0007</t>
+  </si>
+  <si>
+    <t>0.0021,0.9893,0.0731,0.0028</t>
+  </si>
+  <si>
+    <t>0.0057,0.0375,0.9738,0.0152</t>
+  </si>
+  <si>
+    <t>0.0039,0.0466,0.9805,0.0079</t>
+  </si>
+  <si>
+    <t>0.0740,0.0085,0.9504,0.0084</t>
+  </si>
+  <si>
+    <t>0.0307,0.0018,0.9817,0.0054</t>
+  </si>
+  <si>
+    <t>0.0032,0.0041,0.9925,0.0052</t>
+  </si>
+  <si>
+    <t>0.0715,0.1897,0.8339,0.0185</t>
+  </si>
+  <si>
+    <t>0.9565,0.0437,0.0096,0.0041</t>
+  </si>
+  <si>
+    <t>0.9512,0.0159,0.0145,0.0105</t>
+  </si>
+  <si>
+    <t>0.9480,0.0051,0.0061,0.0234</t>
+  </si>
+  <si>
+    <t>0.1377,0.0367,0.8940,0.0252</t>
+  </si>
+  <si>
+    <t>0.9741,0.0062,0.0056,0.0049</t>
+  </si>
+  <si>
+    <t>0.9729,0.0083,0.0078,0.0056</t>
+  </si>
+  <si>
+    <t>0.9518,0.0606,0.0067,0.0021</t>
+  </si>
+  <si>
+    <t>0.0066,0.8081,0.8704,0.0046</t>
+  </si>
+  <si>
+    <t>0.0291,0.0920,0.9430,0.0170</t>
+  </si>
+  <si>
+    <t>0.0280,0.0980,0.9081,0.0285</t>
+  </si>
+  <si>
+    <t>0.0022,0.9670,0.7551,0.0012</t>
+  </si>
+  <si>
+    <t>0.0059,0.0041,0.9892,0.0061</t>
+  </si>
+  <si>
+    <t>0.1069,0.8605,0.0630,0.0118</t>
+  </si>
+  <si>
+    <t>0.0450,0.9583,0.0066,0.0011</t>
+  </si>
+  <si>
+    <t>0.7912,0.0090,0.2566,0.0169</t>
+  </si>
+  <si>
+    <t>0.7011,0.0516,0.3033,0.0121</t>
+  </si>
+  <si>
+    <t>0.0233,0.0443,0.9507,0.0190</t>
+  </si>
+  <si>
+    <t>0.0067,0.9578,0.3551,0.0019</t>
+  </si>
+  <si>
+    <t>0.0258,0.8999,0.3850,0.0093</t>
+  </si>
+  <si>
+    <t>0.0080,0.9808,0.0326,0.0022</t>
+  </si>
+  <si>
+    <t>0.0115,0.9246,0.5594,0.0056</t>
+  </si>
+  <si>
+    <t>0.0292,0.0034,0.0169,0.9706</t>
+  </si>
+  <si>
+    <t>0.0048,0.0047,0.0007,0.9966</t>
+  </si>
+  <si>
+    <t>0.0042,0.0124,0.0002,0.9972</t>
+  </si>
+  <si>
+    <t>0.2695,0.0114,0.0109,0.8454</t>
+  </si>
+  <si>
+    <t>0.0311,0.0153,0.0118,0.9734</t>
+  </si>
+  <si>
+    <t>0.0350,0.0072,0.0036,0.9795</t>
+  </si>
+  <si>
+    <t>0.0140,0.8673,0.6408,0.0050</t>
+  </si>
+  <si>
+    <t>0.0140,0.8507,0.6914,0.0039</t>
+  </si>
+  <si>
+    <t>0.0223,0.3555,0.8409,0.0081</t>
+  </si>
+  <si>
+    <t>0.0346,0.5208,0.8401,0.0111</t>
+  </si>
+  <si>
+    <t>0.0057,0.9265,0.6028,0.0024</t>
+  </si>
+  <si>
+    <t>0.0162,0.9193,0.4958,0.0072</t>
+  </si>
+  <si>
+    <t>0.9852,0.0021,0.0012,0.0050</t>
+  </si>
+  <si>
+    <t>0.9793,0.0107,0.0024,0.0034</t>
+  </si>
+  <si>
+    <t>0.9679,0.0140,0.0040,0.0063</t>
+  </si>
+  <si>
+    <t>0.9779,0.0063,0.0019,0.0054</t>
+  </si>
+  <si>
+    <t>0.9815,0.0066,0.0020,0.0036</t>
+  </si>
+  <si>
+    <t>0.9791,0.0032,0.0018,0.0063</t>
+  </si>
+  <si>
+    <t>0.9767,0.0056,0.0014,0.0066</t>
+  </si>
+  <si>
+    <t>0.9588,0.0202,0.0053,0.0122</t>
+  </si>
+  <si>
+    <t>0.9804,0.0016,0.0007,0.0088</t>
+  </si>
+  <si>
+    <t>0.9821,0.0022,0.0042,0.0045</t>
+  </si>
+  <si>
+    <t>0.9866,0.0012,0.0008,0.0054</t>
+  </si>
+  <si>
+    <t>0.9893,0.0008,0.0005,0.0048</t>
+  </si>
+  <si>
+    <t>0.9841,0.0050,0.0017,0.0033</t>
+  </si>
+  <si>
+    <t>0.9702,0.0092,0.0032,0.0081</t>
+  </si>
+  <si>
+    <t>0.9885,0.0031,0.0021,0.0017</t>
+  </si>
+  <si>
+    <t>0.9897,0.0012,0.0005,0.0036</t>
+  </si>
+  <si>
+    <t>0.0188,0.0064,0.9802,0.0086</t>
+  </si>
+  <si>
+    <t>0.0115,0.0018,0.9897,0.0046</t>
+  </si>
+  <si>
+    <t>0.7251,0.0349,0.0676,0.2078</t>
+  </si>
+  <si>
+    <t>0.0086,0.0016,0.9820,0.0185</t>
+  </si>
+  <si>
+    <t>0.0207,0.9692,0.0160,0.0026</t>
+  </si>
+  <si>
+    <t>0.0551,0.9450,0.0208,0.0026</t>
+  </si>
+  <si>
+    <t>0.1481,0.8837,0.0072,0.0024</t>
+  </si>
+  <si>
+    <t>0.0583,0.9519,0.0048,0.0016</t>
+  </si>
+  <si>
+    <t>0.0067,0.9878,0.0148,0.0019</t>
+  </si>
+  <si>
+    <t>0.0048,0.9906,0.0032,0.0014</t>
+  </si>
+  <si>
+    <t>0.6726,0.3552,0.0199,0.0014</t>
+  </si>
+  <si>
+    <t>0.3662,0.2069,0.2741,0.3262</t>
+  </si>
+  <si>
+    <t>0.3097,0.0537,0.7382,0.0231</t>
+  </si>
+  <si>
+    <t>0.3473,0.1154,0.4597,0.1932</t>
+  </si>
+  <si>
+    <t>0.4874,0.0479,0.4587,0.1016</t>
+  </si>
+  <si>
+    <t>0.1590,0.0341,0.1331,0.8016</t>
+  </si>
+  <si>
+    <t>0.0007,0.9968,0.0084,0.0013</t>
+  </si>
+  <si>
+    <t>0.0013,0.9874,0.0216,0.0211</t>
+  </si>
+  <si>
+    <t>0.0009,0.9897,0.0083,0.0203</t>
+  </si>
+  <si>
+    <t>0.0010,0.9939,0.0653,0.0026</t>
+  </si>
+  <si>
+    <t>0.0962,0.8726,0.1054,0.0028</t>
+  </si>
+  <si>
+    <t>0.8441,0.1674,0.0301,0.0056</t>
+  </si>
+  <si>
+    <t>0.8002,0.1422,0.0760,0.0106</t>
+  </si>
+  <si>
+    <t>0.9781,0.0053,0.0049,0.0046</t>
+  </si>
+  <si>
+    <t>0.9732,0.0010,0.0008,0.0221</t>
+  </si>
+  <si>
+    <t>0.9535,0.0058,0.0106,0.0128</t>
+  </si>
+  <si>
+    <t>0.9446,0.0142,0.0370,0.0067</t>
+  </si>
+  <si>
+    <t>0.9874,0.0003,0.0003,0.0103</t>
+  </si>
+  <si>
+    <t>0.9742,0.0043,0.0045,0.0078</t>
+  </si>
+  <si>
+    <t>0.9433,0.0071,0.0198,0.0171</t>
+  </si>
+  <si>
+    <t>0.9765,0.0040,0.0060,0.0045</t>
+  </si>
+  <si>
+    <t>0.0042,0.5707,0.9279,0.0020</t>
+  </si>
+  <si>
+    <t>0.0268,0.4789,0.8165,0.0084</t>
+  </si>
+  <si>
+    <t>0.0046,0.0429,0.9784,0.0040</t>
+  </si>
+  <si>
+    <t>0.0598,0.0567,0.9088,0.0123</t>
+  </si>
+  <si>
+    <t>0.8459,0.0260,0.1226,0.0070</t>
+  </si>
+  <si>
+    <t>0.6141,0.0232,0.0683,0.2832</t>
+  </si>
+  <si>
+    <t>0.0923,0.0045,0.9632,0.0059</t>
+  </si>
+  <si>
+    <t>0.5543,0.0703,0.4313,0.0603</t>
+  </si>
+  <si>
+    <t>0.0839,0.0039,0.0087,0.9504</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.0001,0.9998</t>
+  </si>
+  <si>
+    <t>0.0024,0.0029,0.0007,0.9980</t>
+  </si>
+  <si>
+    <t>0.0075,0.0013,0.0022,0.9943</t>
+  </si>
+  <si>
+    <t>0.0151,0.8867,0.6321,0.0121</t>
+  </si>
+  <si>
+    <t>0.9677,0.0175,0.0072,0.0037</t>
+  </si>
+  <si>
+    <t>0.4421,0.5661,0.0713,0.0226</t>
+  </si>
+  <si>
+    <t>0.9700,0.0073,0.0043,0.0098</t>
+  </si>
+  <si>
+    <t>0.6048,0.4427,0.0436,0.0197</t>
+  </si>
+  <si>
+    <t>0.9860,0.0023,0.0019,0.0033</t>
+  </si>
+  <si>
+    <t>0.5403,0.0071,0.2996,0.0926</t>
+  </si>
+  <si>
+    <t>0.9449,0.0071,0.0110,0.0207</t>
+  </si>
+  <si>
+    <t>0.0149,0.2106,0.9191,0.0503</t>
+  </si>
+  <si>
+    <t>0.9005,0.0017,0.0065,0.0762</t>
+  </si>
+  <si>
+    <t>0.8255,0.0013,0.0093,0.1251</t>
+  </si>
+  <si>
+    <t>0.5953,0.3445,0.0873,0.0165</t>
+  </si>
+  <si>
+    <t>0.8571,0.0325,0.0884,0.0209</t>
+  </si>
+  <si>
+    <t>0.9089,0.0380,0.0367,0.0138</t>
+  </si>
+  <si>
+    <t>0.0789,0.8438,0.1002,0.0717</t>
+  </si>
+  <si>
+    <t>0.7194,0.0799,0.2065,0.0131</t>
+  </si>
+  <si>
+    <t>0.9093,0.0426,0.0402,0.0094</t>
+  </si>
+  <si>
+    <t>0.9632,0.0031,0.0022,0.0200</t>
+  </si>
+  <si>
+    <t>0.9769,0.0068,0.0029,0.0058</t>
+  </si>
+  <si>
+    <t>0.9835,0.0015,0.0029,0.0048</t>
+  </si>
+  <si>
+    <t>0.9736,0.0010,0.0016,0.0160</t>
+  </si>
+  <si>
+    <t>0.9888,0.0021,0.0028,0.0015</t>
+  </si>
+  <si>
+    <t>0.9803,0.0046,0.0053,0.0035</t>
+  </si>
+  <si>
+    <t>0.9758,0.0021,0.0066,0.0058</t>
+  </si>
+  <si>
+    <t>0.9877,0.0016,0.0012,0.0042</t>
+  </si>
+  <si>
+    <t>0.6570,0.3169,0.0622,0.0085</t>
+  </si>
+  <si>
+    <t>0.6987,0.3015,0.0352,0.0056</t>
+  </si>
+  <si>
+    <t>0.8166,0.2055,0.0154,0.0022</t>
+  </si>
+  <si>
+    <t>0.7807,0.1047,0.1072,0.0308</t>
+  </si>
+  <si>
+    <t>0.9770,0.0121,0.0018,0.0031</t>
+  </si>
+  <si>
+    <t>0.9541,0.0082,0.0333,0.0021</t>
+  </si>
+  <si>
+    <t>0.9666,0.0102,0.0034,0.0087</t>
+  </si>
+  <si>
+    <t>0.9523,0.0054,0.0088,0.0162</t>
+  </si>
+  <si>
+    <t>0.0066,0.0118,0.9933,0.0017</t>
+  </si>
+  <si>
+    <t>0.9474,0.0187,0.0162,0.0121</t>
+  </si>
+  <si>
+    <t>0.0018,0.0013,0.9963,0.0022</t>
+  </si>
+  <si>
+    <t>0.0352,0.0333,0.9538,0.0129</t>
+  </si>
+  <si>
+    <t>0.0158,0.0021,0.9873,0.0032</t>
+  </si>
+  <si>
+    <t>0.1814,0.4746,0.5582,0.0446</t>
+  </si>
+  <si>
+    <t>0.0730,0.0099,0.9382,0.0201</t>
+  </si>
+  <si>
+    <t>0.0060,0.0021,0.9932,0.0012</t>
+  </si>
+  <si>
+    <t>0.0166,0.0146,0.9755,0.0067</t>
+  </si>
+  <si>
+    <t>0.2850,0.0629,0.7325,0.0200</t>
+  </si>
+  <si>
+    <t>0.3228,0.0397,0.7504,0.0122</t>
+  </si>
+  <si>
+    <t>0.7092,0.0209,0.3350,0.0052</t>
+  </si>
+  <si>
+    <t>0.2185,0.0946,0.6750,0.0115</t>
+  </si>
+  <si>
+    <t>0.4548,0.3321,0.2567,0.0443</t>
+  </si>
+  <si>
+    <t>0.3443,0.0809,0.5687,0.0051</t>
+  </si>
+  <si>
+    <t>0.6637,0.1100,0.1278,0.1240</t>
+  </si>
+  <si>
+    <t>0.2055,0.2288,0.5876,0.0656</t>
+  </si>
+  <si>
+    <t>0.5211,0.5280,0.0272,0.0049</t>
+  </si>
+  <si>
+    <t>0.7393,0.3582,0.0120,0.0028</t>
+  </si>
+  <si>
+    <t>0.5867,0.4852,0.0165,0.0163</t>
+  </si>
+  <si>
+    <t>0.9627,0.0267,0.0051,0.0054</t>
+  </si>
+  <si>
+    <t>0.4848,0.6471,0.0141,0.0037</t>
+  </si>
+  <si>
+    <t>0.5965,0.1258,0.3199,0.0427</t>
+  </si>
+  <si>
+    <t>0.8723,0.0078,0.0770,0.0183</t>
+  </si>
+  <si>
+    <t>0.1448,0.0289,0.0232,0.8862</t>
+  </si>
+  <si>
+    <t>0.9108,0.0186,0.0598,0.0036</t>
+  </si>
+  <si>
+    <t>0.3003,0.0157,0.3875,0.3188</t>
+  </si>
+  <si>
+    <t>0.1305,0.0091,0.9083,0.0221</t>
+  </si>
+  <si>
+    <t>0.3114,0.2864,0.4198,0.1391</t>
+  </si>
+  <si>
+    <t>0.0537,0.0230,0.8909,0.0728</t>
+  </si>
+  <si>
+    <t>0.0169,0.0183,0.9613,0.0193</t>
+  </si>
+  <si>
+    <t>0.0578,0.4556,0.7016,0.0185</t>
+  </si>
+  <si>
+    <t>0.9682,0.0019,0.0013,0.0212</t>
+  </si>
+  <si>
+    <t>0.9875,0.0036,0.0025,0.0018</t>
+  </si>
+  <si>
+    <t>0.9760,0.0128,0.0028,0.0039</t>
+  </si>
+  <si>
+    <t>0.9668,0.0164,0.0137,0.0033</t>
+  </si>
+  <si>
+    <t>0.9701,0.0175,0.0054,0.0048</t>
+  </si>
+  <si>
+    <t>0.9801,0.0052,0.0045,0.0039</t>
+  </si>
+  <si>
+    <t>0.9799,0.0043,0.0026,0.0060</t>
+  </si>
+  <si>
+    <t>0.9828,0.0044,0.0024,0.0049</t>
+  </si>
+  <si>
+    <t>0.0273,0.0059,0.9813,0.0081</t>
+  </si>
+  <si>
+    <t>0.2439,0.1589,0.7034,0.0252</t>
+  </si>
+  <si>
+    <t>0.9114,0.0226,0.0463,0.0149</t>
+  </si>
+  <si>
+    <t>0.0047,0.0036,0.9923,0.0024</t>
+  </si>
+  <si>
+    <t>0.0045,0.0044,0.9849,0.0143</t>
+  </si>
+  <si>
+    <t>0.0517,0.1732,0.8223,0.0160</t>
+  </si>
+  <si>
+    <t>0.0100,0.0066,0.9878,0.0044</t>
+  </si>
+  <si>
+    <t>0.0856,0.0313,0.9108,0.0130</t>
+  </si>
+  <si>
+    <t>0.0079,0.0132,0.9855,0.0064</t>
+  </si>
+  <si>
+    <t>0.0178,0.0095,0.9727,0.0132</t>
+  </si>
+  <si>
+    <t>0.0959,0.0783,0.8579,0.0221</t>
+  </si>
+  <si>
+    <t>0.6212,0.0136,0.4874,0.0104</t>
+  </si>
+  <si>
+    <t>0.8378,0.0166,0.0952,0.0377</t>
+  </si>
+  <si>
+    <t>0.8710,0.0082,0.0929,0.0093</t>
+  </si>
+  <si>
+    <t>0.9752,0.0097,0.0026,0.0060</t>
+  </si>
+  <si>
+    <t>0.9833,0.0049,0.0024,0.0030</t>
+  </si>
+  <si>
+    <t>0.9849,0.0036,0.0008,0.0034</t>
+  </si>
+  <si>
+    <t>0.9734,0.0138,0.0032,0.0045</t>
+  </si>
+  <si>
+    <t>0.9679,0.0056,0.0045,0.0090</t>
+  </si>
+  <si>
+    <t>0.9773,0.0063,0.0024,0.0058</t>
+  </si>
+  <si>
+    <t>0.9757,0.0143,0.0049,0.0033</t>
+  </si>
+  <si>
+    <t>0.9741,0.0068,0.0020,0.0082</t>
+  </si>
+  <si>
+    <t>0.0806,0.6426,0.5013,0.0318</t>
+  </si>
+  <si>
+    <t>0.0082,0.0852,0.9718,0.0023</t>
+  </si>
+  <si>
+    <t>0.0098,0.0150,0.9815,0.0052</t>
+  </si>
+  <si>
+    <t>0.0833,0.0154,0.9243,0.0178</t>
+  </si>
+  <si>
+    <t>0.0219,0.0063,0.9811,0.0042</t>
+  </si>
+  <si>
+    <t>0.3327,0.0064,0.5648,0.1102</t>
+  </si>
+  <si>
+    <t>0.0639,0.0070,0.9534,0.0162</t>
+  </si>
+  <si>
+    <t>0.3169,0.1186,0.5882,0.0672</t>
+  </si>
+  <si>
+    <t>0.1590,0.0016,0.0014,0.9420</t>
+  </si>
+  <si>
+    <t>0.0135,0.0909,0.0024,0.9820</t>
+  </si>
+  <si>
+    <t>0.3631,0.0157,0.0018,0.7983</t>
+  </si>
+  <si>
+    <t>0.0013,0.0039,0.0001,0.9989</t>
+  </si>
+  <si>
+    <t>0.0010,0.0006,0.0001,0.9995</t>
+  </si>
+  <si>
+    <t>0.6698,0.0682,0.0252,0.2741</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2177,7 +2177,7 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D18" t="s">
         <v>280</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2233,7 +2233,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2247,7 +2247,7 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
         <v>285</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2373,7 +2373,7 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
         <v>294</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2639,7 +2639,7 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
         <v>313</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3451,7 +3451,7 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
         <v>371</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3521,7 +3521,7 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D114" t="s">
         <v>376</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4529,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
         <v>448</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4655,7 +4655,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
         <v>457</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4753,7 +4753,7 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
         <v>464</v>
@@ -4795,7 +4795,7 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D205" t="s">
         <v>467</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5439,7 +5439,7 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
         <v>513</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
